--- a/Intership/target_companies.xlsx
+++ b/Intership/target_companies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\OneDrive\Documenten\OneDrive\Hero Claude\Intership\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22C43262-8D5C-460A-8D4F-5686AC5B74B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BEC8DCC-678E-4D28-9F50-6C51D41891FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{8D3D2CB7-5210-4F38-920B-947314EC033B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{E407F25F-2BE1-42E2-A993-7D011CA40CFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Target Companies" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="93">
   <si>
     <t>Industry</t>
   </si>
@@ -116,7 +116,7 @@
     <t>Adidas</t>
   </si>
   <si>
-    <t>European operations hub</t>
+    <t>SPECIFIC OPENING: Intern Buying eCommerce — Sep 2026 EUR 1200/mo</t>
   </si>
   <si>
     <t>Decathlon</t>
@@ -137,7 +137,7 @@
     <t>Leusden/Amsterdam</t>
   </si>
   <si>
-    <t>Importer of VW, Audi, Porsche, Bentley</t>
+    <t>Importer of VW Audi Porsche Bentley</t>
   </si>
   <si>
     <t>Stellantis</t>
@@ -152,7 +152,7 @@
     <t>Amsterdam/Tilburg</t>
   </si>
   <si>
-    <t>Fast-growing with logistics ops</t>
+    <t>EV leader — strong personal interest logistics &amp; supply chain ops</t>
   </si>
   <si>
     <t>DAF Trucks</t>
@@ -168,6 +168,75 @@
   </si>
   <si>
     <t>Premium automotive</t>
+  </si>
+  <si>
+    <t>Automotive (EV)</t>
+  </si>
+  <si>
+    <t>Polestar</t>
+  </si>
+  <si>
+    <t>Beesd (Hybrid)</t>
+  </si>
+  <si>
+    <t>SPECIFIC OPENING: Marketing &amp; Events Intern — Sep 2026</t>
+  </si>
+  <si>
+    <t>Fastned</t>
+  </si>
+  <si>
+    <t>EV charging infrastructure — logistics &amp; operations</t>
+  </si>
+  <si>
+    <t>Ebusco</t>
+  </si>
+  <si>
+    <t>Deurne</t>
+  </si>
+  <si>
+    <t>Dutch electric bus manufacturer — supply chain</t>
+  </si>
+  <si>
+    <t>Jedlix</t>
+  </si>
+  <si>
+    <t>Rotterdam area</t>
+  </si>
+  <si>
+    <t>Smart EV charging platform — close to Rotterdam</t>
+  </si>
+  <si>
+    <t>Rivian</t>
+  </si>
+  <si>
+    <t>Amsterdam (EU office)</t>
+  </si>
+  <si>
+    <t>US EV brand with Netherlands presence</t>
+  </si>
+  <si>
+    <t>BYD Europe</t>
+  </si>
+  <si>
+    <t>Fastest growing EV brand in Europe — supply chain ops</t>
+  </si>
+  <si>
+    <t>Lightyear</t>
+  </si>
+  <si>
+    <t>Helmond</t>
+  </si>
+  <si>
+    <t>Dutch solar EV startup — innovative supply chain</t>
+  </si>
+  <si>
+    <t>ENZA Motors</t>
+  </si>
+  <si>
+    <t>Dordrecht</t>
+  </si>
+  <si>
+    <t>Dutch EV startup very close to Rotterdam</t>
   </si>
   <si>
     <t>Food</t>
@@ -301,13 +370,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D9E332E1-50CC-4797-9015-3BA2EB2C36F6}" name="TargetCompanies" displayName="TargetCompanies" ref="A1:D26" totalsRowShown="0">
-  <autoFilter ref="A1:D26" xr:uid="{D9E332E1-50CC-4797-9015-3BA2EB2C36F6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95AD53A3-4D7C-4A05-B572-EEE9EE780597}" name="TargetCompanies" displayName="TargetCompanies" ref="A1:D34" totalsRowShown="0">
+  <autoFilter ref="A1:D34" xr:uid="{95AD53A3-4D7C-4A05-B572-EEE9EE780597}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{78C99E65-18E5-4C47-996E-4E3AA6ED849D}" name="Industry"/>
-    <tableColumn id="2" xr3:uid="{CD75A0B5-6CF8-44E8-8C84-228379DFD591}" name="Company"/>
-    <tableColumn id="3" xr3:uid="{2BC49C65-F57C-43DE-ABAA-9C99CACA9FDE}" name="Location"/>
-    <tableColumn id="4" xr3:uid="{7DF85747-1369-4BE1-93DE-D32EEFC0C85B}" name="Notes"/>
+    <tableColumn id="1" xr3:uid="{707E8C9F-22AE-4586-9297-9AB6B0952027}" name="Industry"/>
+    <tableColumn id="2" xr3:uid="{8E2D4C1E-F98D-4EDD-B670-1E52ABB9B88A}" name="Company"/>
+    <tableColumn id="3" xr3:uid="{87219712-B145-453C-9B34-8CDE0105459B}" name="Location"/>
+    <tableColumn id="4" xr3:uid="{3EAAE506-D1C7-4EB3-97BD-1F317F3BF462}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -629,14 +698,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B3CB9D9-4926-4F02-810D-512B4375230B}">
-  <dimension ref="A1:D26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D7012A0-18A7-4593-AA25-78580431F126}">
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="60.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -871,10 +940,10 @@
         <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -882,13 +951,13 @@
         <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -896,13 +965,13 @@
         <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -910,13 +979,13 @@
         <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -924,83 +993,195 @@
         <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
         <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
